--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N70_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>66.4933818636799</v>
+        <v>10.80517455284798</v>
       </c>
       <c r="D2" t="n">
-        <v>66.3107311885113</v>
+        <v>10.77549381813309</v>
       </c>
       <c r="E2" t="n">
-        <v>13.80192366007637</v>
+        <v>2.242812594762409</v>
       </c>
       <c r="F2" t="n">
-        <v>13.64774726198316</v>
+        <v>2.217758930072264</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.88953454352717</v>
+        <v>6.319549363323166</v>
       </c>
       <c r="D3" t="n">
-        <v>39.01523666454497</v>
+        <v>6.339975957988558</v>
       </c>
       <c r="E3" t="n">
-        <v>13.80192366007637</v>
+        <v>2.242812594762409</v>
       </c>
       <c r="F3" t="n">
-        <v>13.64774726198316</v>
+        <v>2.217758930072264</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
